--- a/artfynd/A 55712-2021 artfynd.xlsx
+++ b/artfynd/A 55712-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55712-2021 artfynd.xlsx
+++ b/artfynd/A 55712-2021 artfynd.xlsx
@@ -675,57 +675,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>83654506</v>
+        <v>97291711</v>
       </c>
       <c r="B2" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223246</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>BORÅS 17, Vg</t>
+          <t>170 m söder Björkesbacken, Järnvägsstation  Viskafors, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>369639.9542871232</v>
+        <v>369508</v>
       </c>
       <c r="R2" t="n">
-        <v>6386989.641115025</v>
+        <v>6386967</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,34 +750,29 @@
           <t>Seglora</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>17851E3B-15E0-4637-999C-7782FB9A5CAD</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-03-27</t>
+          <t>2021-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-03-27</t>
+          <t>2021-11-17</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Inventerat av: Skogsstyrelsen (SAFT) {B1F2B9F9-779E-4DD8-896B-8D0FE397E7A6}</t>
+          <t>På åsrygg. Överslag av antal men räknade ganska noga.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,87 +781,71 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna Stenström</t>
+          <t>Per Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Stenström</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Per Johansson, Sophie Gröndahl</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97291711</v>
+        <v>83654506</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>223246</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1300</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>170 m söder Björkesbacken, Järnvägsstation  Viskafors, Vg</t>
+          <t>BORÅS 17, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>369508.1531027963</v>
+        <v>369640</v>
       </c>
       <c r="R3" t="n">
-        <v>6386967.075369343</v>
+        <v>6386990</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,29 +867,24 @@
           <t>Seglora</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>17851E3B-15E0-4637-999C-7782FB9A5CAD</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-11-17</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2014-03-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-11-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2014-03-27</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På åsrygg. Överslag av antal men räknade ganska noga.</t>
+          <t>Inventerat av: Skogsstyrelsen (SAFT) {B1F2B9F9-779E-4DD8-896B-8D0FE397E7A6}</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,22 +893,25 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Per Johansson</t>
+          <t>Anna Stenström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Johansson, Sophie Gröndahl</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Anna Stenström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55712-2021 artfynd.xlsx
+++ b/artfynd/A 55712-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97291711</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,8 +922,17 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83654506</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>